--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_09.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_09.xlsx
@@ -480,25 +480,25 @@
         <v>45901</v>
       </c>
       <c r="B5" t="n">
-        <v>1459.27</v>
+        <v>1466.78</v>
       </c>
       <c r="C5" t="n">
         <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>1064.38</v>
+        <v>1050.48</v>
       </c>
       <c r="E5" t="n">
-        <v>283.43</v>
+        <v>287.24</v>
       </c>
       <c r="F5" t="n">
-        <v>2004</v>
+        <v>1402</v>
       </c>
       <c r="G5" t="n">
-        <v>390129</v>
+        <v>373574</v>
       </c>
       <c r="H5" t="n">
-        <v>65610</v>
+        <v>64759</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45902</v>
       </c>
       <c r="B6" t="n">
-        <v>1492.67</v>
+        <v>1489.57</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>23.14</v>
       </c>
       <c r="D6" t="n">
-        <v>1087.83</v>
+        <v>1079.74</v>
       </c>
       <c r="E6" t="n">
-        <v>300.06</v>
+        <v>292.38</v>
       </c>
       <c r="F6" t="n">
-        <v>1845</v>
+        <v>1448</v>
       </c>
       <c r="G6" t="n">
-        <v>439337</v>
+        <v>396196</v>
       </c>
       <c r="H6" t="n">
-        <v>65780</v>
+        <v>66073</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45903</v>
       </c>
       <c r="B7" t="n">
-        <v>1381.78</v>
+        <v>1517.4</v>
       </c>
       <c r="C7" t="n">
-        <v>22.07</v>
+        <v>23.47</v>
       </c>
       <c r="D7" t="n">
-        <v>1005.93</v>
+        <v>1102.06</v>
       </c>
       <c r="E7" t="n">
-        <v>268.62</v>
+        <v>297.26</v>
       </c>
       <c r="F7" t="n">
-        <v>1809</v>
+        <v>1553</v>
       </c>
       <c r="G7" t="n">
-        <v>367140</v>
+        <v>423940</v>
       </c>
       <c r="H7" t="n">
-        <v>64765</v>
+        <v>69341</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45904</v>
       </c>
       <c r="B8" t="n">
-        <v>1283.28</v>
+        <v>1476.63</v>
       </c>
       <c r="C8" t="n">
-        <v>21.18</v>
+        <v>24</v>
       </c>
       <c r="D8" t="n">
-        <v>932.14</v>
+        <v>1063.29</v>
       </c>
       <c r="E8" t="n">
-        <v>259.43</v>
+        <v>291.17</v>
       </c>
       <c r="F8" t="n">
-        <v>1794</v>
+        <v>1385</v>
       </c>
       <c r="G8" t="n">
-        <v>348168</v>
+        <v>367662</v>
       </c>
       <c r="H8" t="n">
-        <v>56988</v>
+        <v>61979</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45905</v>
       </c>
       <c r="B9" t="n">
-        <v>700.96</v>
+        <v>1484.51</v>
       </c>
       <c r="C9" t="n">
-        <v>12.12</v>
+        <v>23.01</v>
       </c>
       <c r="D9" t="n">
-        <v>508.93</v>
+        <v>1080.44</v>
       </c>
       <c r="E9" t="n">
-        <v>136.54</v>
+        <v>291.14</v>
       </c>
       <c r="F9" t="n">
-        <v>1525</v>
+        <v>1425</v>
       </c>
       <c r="G9" t="n">
-        <v>206643</v>
+        <v>370561</v>
       </c>
       <c r="H9" t="n">
-        <v>32417</v>
+        <v>65626</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45906</v>
       </c>
       <c r="B10" t="n">
-        <v>1343.67</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>21.2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>967.58</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>263.45</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1922</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>364821</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>60767</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -636,25 +636,25 @@
         <v>45907</v>
       </c>
       <c r="B11" t="n">
-        <v>610.6</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>10.08</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>441.57</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>123.37</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1066</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>175042</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>28992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -662,25 +662,25 @@
         <v>45908</v>
       </c>
       <c r="B12" t="n">
-        <v>500.34</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>7.97</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>364.31</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>101.28</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>907</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>138112</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>23533</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45909</v>
       </c>
       <c r="B13" t="n">
-        <v>1153.45</v>
+        <v>1433.55</v>
       </c>
       <c r="C13" t="n">
-        <v>18.06</v>
+        <v>22.47</v>
       </c>
       <c r="D13" t="n">
-        <v>837.4299999999999</v>
+        <v>1041.48</v>
       </c>
       <c r="E13" t="n">
-        <v>236.13</v>
+        <v>286.9</v>
       </c>
       <c r="F13" t="n">
-        <v>2192</v>
+        <v>1262</v>
       </c>
       <c r="G13" t="n">
-        <v>282404</v>
+        <v>394108</v>
       </c>
       <c r="H13" t="n">
-        <v>52216</v>
+        <v>66411</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45910</v>
       </c>
       <c r="B14" t="n">
-        <v>607.96</v>
+        <v>1542.87</v>
       </c>
       <c r="C14" t="n">
-        <v>9.23</v>
+        <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>441.45</v>
+        <v>1119.14</v>
       </c>
       <c r="E14" t="n">
-        <v>117.64</v>
+        <v>304.77</v>
       </c>
       <c r="F14" t="n">
-        <v>907</v>
+        <v>1460</v>
       </c>
       <c r="G14" t="n">
-        <v>158081</v>
+        <v>384081</v>
       </c>
       <c r="H14" t="n">
-        <v>30853</v>
+        <v>68700</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45911</v>
       </c>
       <c r="B15" t="n">
-        <v>1165.54</v>
+        <v>1427.79</v>
       </c>
       <c r="C15" t="n">
-        <v>18.18</v>
+        <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>845.66</v>
+        <v>1038.17</v>
       </c>
       <c r="E15" t="n">
-        <v>228.76</v>
+        <v>287.13</v>
       </c>
       <c r="F15" t="n">
-        <v>1521</v>
+        <v>1349</v>
       </c>
       <c r="G15" t="n">
-        <v>323115</v>
+        <v>350110</v>
       </c>
       <c r="H15" t="n">
-        <v>52229</v>
+        <v>64220</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45912</v>
       </c>
       <c r="B16" t="n">
-        <v>848.16</v>
+        <v>1518.94</v>
       </c>
       <c r="C16" t="n">
-        <v>12.7</v>
+        <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>621.77</v>
+        <v>1108.59</v>
       </c>
       <c r="E16" t="n">
-        <v>171.49</v>
+        <v>303.05</v>
       </c>
       <c r="F16" t="n">
-        <v>1532</v>
+        <v>1291</v>
       </c>
       <c r="G16" t="n">
-        <v>230480</v>
+        <v>395379</v>
       </c>
       <c r="H16" t="n">
-        <v>35267</v>
+        <v>69035</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45913</v>
       </c>
       <c r="B17" t="n">
-        <v>1511.99</v>
+        <v>178.29</v>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>2.87</v>
       </c>
       <c r="D17" t="n">
-        <v>1087.68</v>
+        <v>129.7</v>
       </c>
       <c r="E17" t="n">
-        <v>298.57</v>
+        <v>35.75</v>
       </c>
       <c r="F17" t="n">
-        <v>2397</v>
+        <v>194</v>
       </c>
       <c r="G17" t="n">
-        <v>371489</v>
+        <v>59195</v>
       </c>
       <c r="H17" t="n">
-        <v>67583</v>
+        <v>7915</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45914</v>
       </c>
       <c r="B18" t="n">
-        <v>1430.88</v>
+        <v>1608</v>
       </c>
       <c r="C18" t="n">
-        <v>23.22</v>
+        <v>24</v>
       </c>
       <c r="D18" t="n">
-        <v>1035.19</v>
+        <v>1159.03</v>
       </c>
       <c r="E18" t="n">
-        <v>289.15</v>
+        <v>318.36</v>
       </c>
       <c r="F18" t="n">
-        <v>2027</v>
+        <v>1484</v>
       </c>
       <c r="G18" t="n">
-        <v>375813</v>
+        <v>481749</v>
       </c>
       <c r="H18" t="n">
-        <v>67216</v>
+        <v>72571</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45915</v>
       </c>
       <c r="B19" t="n">
-        <v>1417.75</v>
+        <v>1508.28</v>
       </c>
       <c r="C19" t="n">
         <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>1032.71</v>
+        <v>1091.16</v>
       </c>
       <c r="E19" t="n">
-        <v>280.51</v>
+        <v>300.13</v>
       </c>
       <c r="F19" t="n">
-        <v>2224</v>
+        <v>1333</v>
       </c>
       <c r="G19" t="n">
-        <v>391199</v>
+        <v>389637</v>
       </c>
       <c r="H19" t="n">
-        <v>61503</v>
+        <v>66527</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45916</v>
       </c>
       <c r="B20" t="n">
-        <v>1587.55</v>
+        <v>1494.54</v>
       </c>
       <c r="C20" t="n">
-        <v>24</v>
+        <v>23.73</v>
       </c>
       <c r="D20" t="n">
-        <v>1154.41</v>
+        <v>1086.45</v>
       </c>
       <c r="E20" t="n">
-        <v>324.95</v>
+        <v>293.13</v>
       </c>
       <c r="F20" t="n">
-        <v>4373</v>
+        <v>1217</v>
       </c>
       <c r="G20" t="n">
-        <v>442006</v>
+        <v>410361</v>
       </c>
       <c r="H20" t="n">
-        <v>69213</v>
+        <v>68416</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45917</v>
       </c>
       <c r="B21" t="n">
-        <v>1482.37</v>
+        <v>1288.51</v>
       </c>
       <c r="C21" t="n">
-        <v>24</v>
+        <v>19.65</v>
       </c>
       <c r="D21" t="n">
-        <v>1071.79</v>
+        <v>930.02</v>
       </c>
       <c r="E21" t="n">
-        <v>296.3</v>
+        <v>257.02</v>
       </c>
       <c r="F21" t="n">
-        <v>2134</v>
+        <v>1412</v>
       </c>
       <c r="G21" t="n">
-        <v>383447</v>
+        <v>344624</v>
       </c>
       <c r="H21" t="n">
-        <v>66662</v>
+        <v>56361</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45918</v>
       </c>
       <c r="B22" t="n">
-        <v>1334.33</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
-        <v>20.56</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>966.47</v>
+        <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>263.65</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1870</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>353984</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>60264</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45919</v>
       </c>
       <c r="B23" t="n">
-        <v>997.08</v>
+        <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>17.15</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>720.42</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>195.39</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>2163</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>279278</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>44796</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45920</v>
       </c>
       <c r="B24" t="n">
-        <v>463.92</v>
+        <v>1360.28</v>
       </c>
       <c r="C24" t="n">
-        <v>7.45</v>
+        <v>22.3</v>
       </c>
       <c r="D24" t="n">
-        <v>333.43</v>
+        <v>991.52</v>
       </c>
       <c r="E24" t="n">
-        <v>90.59</v>
+        <v>265.41</v>
       </c>
       <c r="F24" t="n">
-        <v>788</v>
+        <v>1425</v>
       </c>
       <c r="G24" t="n">
-        <v>123904</v>
+        <v>352445</v>
       </c>
       <c r="H24" t="n">
-        <v>21802</v>
+        <v>66458</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45921</v>
       </c>
       <c r="B25" t="n">
-        <v>1192.4</v>
+        <v>1480.86</v>
       </c>
       <c r="C25" t="n">
-        <v>19.8</v>
+        <v>24</v>
       </c>
       <c r="D25" t="n">
-        <v>868.27</v>
+        <v>1077.16</v>
       </c>
       <c r="E25" t="n">
-        <v>237.1</v>
+        <v>289.26</v>
       </c>
       <c r="F25" t="n">
-        <v>2135</v>
+        <v>1275</v>
       </c>
       <c r="G25" t="n">
-        <v>334104</v>
+        <v>392085</v>
       </c>
       <c r="H25" t="n">
-        <v>53567</v>
+        <v>66249</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>1431.7</v>
+        <v>1294.25</v>
       </c>
       <c r="C26" t="n">
-        <v>24</v>
+        <v>21.39</v>
       </c>
       <c r="D26" t="n">
-        <v>1039.95</v>
+        <v>943.04</v>
       </c>
       <c r="E26" t="n">
-        <v>289.25</v>
+        <v>258.99</v>
       </c>
       <c r="F26" t="n">
-        <v>2125</v>
+        <v>1261</v>
       </c>
       <c r="G26" t="n">
-        <v>375955</v>
+        <v>367149</v>
       </c>
       <c r="H26" t="n">
-        <v>70415</v>
+        <v>58574</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>932.8099999999999</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>15.24</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>678.14</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>190.38</v>
+        <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>1713</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>256734</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>42018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>1358.66</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>23.71</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>976.64</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>274.36</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1872</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>361987</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>59742</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>1455.24</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>1051.84</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
-        <v>294.81</v>
+        <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>1690</v>
+        <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>403896</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>63639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>1216.89</v>
+        <v>1499.55</v>
       </c>
       <c r="C30" t="n">
-        <v>19.89</v>
+        <v>24</v>
       </c>
       <c r="D30" t="n">
-        <v>884.85</v>
+        <v>1085.52</v>
       </c>
       <c r="E30" t="n">
-        <v>242.9</v>
+        <v>301.65</v>
       </c>
       <c r="F30" t="n">
-        <v>1827</v>
+        <v>1474</v>
       </c>
       <c r="G30" t="n">
-        <v>321597</v>
+        <v>379987</v>
       </c>
       <c r="H30" t="n">
-        <v>57774</v>
+        <v>69053</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45927</v>
       </c>
       <c r="B31" t="n">
-        <v>866.09</v>
+        <v>1412.59</v>
       </c>
       <c r="C31" t="n">
-        <v>13.27</v>
+        <v>24</v>
       </c>
       <c r="D31" t="n">
-        <v>633.64</v>
+        <v>1028.53</v>
       </c>
       <c r="E31" t="n">
-        <v>170.28</v>
+        <v>276.29</v>
       </c>
       <c r="F31" t="n">
-        <v>1522</v>
+        <v>1257</v>
       </c>
       <c r="G31" t="n">
-        <v>239523</v>
+        <v>364942</v>
       </c>
       <c r="H31" t="n">
-        <v>39261</v>
+        <v>66014</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45928</v>
       </c>
       <c r="B32" t="n">
-        <v>1383.82</v>
+        <v>1473.54</v>
       </c>
       <c r="C32" t="n">
         <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>1011.39</v>
+        <v>1082.48</v>
       </c>
       <c r="E32" t="n">
-        <v>284.71</v>
+        <v>303.86</v>
       </c>
       <c r="F32" t="n">
-        <v>2475</v>
+        <v>1533</v>
       </c>
       <c r="G32" t="n">
-        <v>366652</v>
+        <v>353842</v>
       </c>
       <c r="H32" t="n">
-        <v>64154</v>
+        <v>66519</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45929</v>
       </c>
       <c r="B33" t="n">
-        <v>790.42</v>
+        <v>1480.07</v>
       </c>
       <c r="C33" t="n">
-        <v>13.15</v>
+        <v>24</v>
       </c>
       <c r="D33" t="n">
-        <v>573.4</v>
+        <v>1076.7</v>
       </c>
       <c r="E33" t="n">
-        <v>155.59</v>
+        <v>294.36</v>
       </c>
       <c r="F33" t="n">
-        <v>1578</v>
+        <v>1645</v>
       </c>
       <c r="G33" t="n">
-        <v>215649</v>
+        <v>416568</v>
       </c>
       <c r="H33" t="n">
-        <v>34679</v>
+        <v>65290</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45930</v>
       </c>
       <c r="B34" t="n">
-        <v>840.29</v>
+        <v>808.7</v>
       </c>
       <c r="C34" t="n">
         <v>13.69</v>
       </c>
       <c r="D34" t="n">
-        <v>611.92</v>
+        <v>591.36</v>
       </c>
       <c r="E34" t="n">
-        <v>165.99</v>
+        <v>164.27</v>
       </c>
       <c r="F34" t="n">
-        <v>1397</v>
+        <v>976</v>
       </c>
       <c r="G34" t="n">
-        <v>269589</v>
+        <v>215502</v>
       </c>
       <c r="H34" t="n">
-        <v>37644</v>
+        <v>33949</v>
       </c>
     </row>
     <row r="36">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34241.87</v>
+        <v>30245.5</v>
       </c>
       <c r="C36" t="n">
-        <v>555.92</v>
+        <v>483.72</v>
       </c>
       <c r="D36" t="n">
-        <v>24851.12</v>
+        <v>21956.06</v>
       </c>
       <c r="E36" t="n">
-        <v>6834.679999999999</v>
+        <v>5999.52</v>
       </c>
       <c r="F36" t="n">
-        <v>55334</v>
+        <v>29061</v>
       </c>
       <c r="G36" t="n">
-        <v>9290278</v>
+        <v>7983697</v>
       </c>
       <c r="H36" t="n">
-        <v>1551349</v>
+        <v>1360040</v>
       </c>
     </row>
   </sheetData>

--- a/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_09.xlsx
+++ b/00-esmagadora-modelo/dados_sujos/apontamentos_mensais/producao_2025_09.xlsx
@@ -480,25 +480,25 @@
         <v>45901</v>
       </c>
       <c r="B5" t="n">
-        <v>1466.78</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>1050.48</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>287.24</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>1402</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>373574</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>64759</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -506,25 +506,25 @@
         <v>45902</v>
       </c>
       <c r="B6" t="n">
-        <v>1489.57</v>
+        <v>1576.7</v>
       </c>
       <c r="C6" t="n">
-        <v>23.14</v>
+        <v>24</v>
       </c>
       <c r="D6" t="n">
-        <v>1079.74</v>
+        <v>1130.98</v>
       </c>
       <c r="E6" t="n">
-        <v>292.38</v>
+        <v>320.07</v>
       </c>
       <c r="F6" t="n">
-        <v>1448</v>
+        <v>1521</v>
       </c>
       <c r="G6" t="n">
-        <v>396196</v>
+        <v>447234</v>
       </c>
       <c r="H6" t="n">
-        <v>66073</v>
+        <v>71838</v>
       </c>
     </row>
     <row r="7">
@@ -532,25 +532,25 @@
         <v>45903</v>
       </c>
       <c r="B7" t="n">
-        <v>1517.4</v>
+        <v>1562.52</v>
       </c>
       <c r="C7" t="n">
-        <v>23.47</v>
+        <v>24</v>
       </c>
       <c r="D7" t="n">
-        <v>1102.06</v>
+        <v>1125.39</v>
       </c>
       <c r="E7" t="n">
-        <v>297.26</v>
+        <v>314.68</v>
       </c>
       <c r="F7" t="n">
-        <v>1553</v>
+        <v>1296</v>
       </c>
       <c r="G7" t="n">
-        <v>423940</v>
+        <v>412798</v>
       </c>
       <c r="H7" t="n">
-        <v>69341</v>
+        <v>72396</v>
       </c>
     </row>
     <row r="8">
@@ -558,25 +558,25 @@
         <v>45904</v>
       </c>
       <c r="B8" t="n">
-        <v>1476.63</v>
+        <v>1440.76</v>
       </c>
       <c r="C8" t="n">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="D8" t="n">
-        <v>1063.29</v>
+        <v>1038.35</v>
       </c>
       <c r="E8" t="n">
-        <v>291.17</v>
+        <v>293.84</v>
       </c>
       <c r="F8" t="n">
-        <v>1385</v>
+        <v>1371</v>
       </c>
       <c r="G8" t="n">
-        <v>367662</v>
+        <v>399559</v>
       </c>
       <c r="H8" t="n">
-        <v>61979</v>
+        <v>64201</v>
       </c>
     </row>
     <row r="9">
@@ -584,25 +584,25 @@
         <v>45905</v>
       </c>
       <c r="B9" t="n">
-        <v>1484.51</v>
+        <v>1425.06</v>
       </c>
       <c r="C9" t="n">
-        <v>23.01</v>
+        <v>23.67</v>
       </c>
       <c r="D9" t="n">
-        <v>1080.44</v>
+        <v>1026.44</v>
       </c>
       <c r="E9" t="n">
-        <v>291.14</v>
+        <v>289.67</v>
       </c>
       <c r="F9" t="n">
-        <v>1425</v>
+        <v>1049</v>
       </c>
       <c r="G9" t="n">
-        <v>370561</v>
+        <v>383890</v>
       </c>
       <c r="H9" t="n">
-        <v>65626</v>
+        <v>66152</v>
       </c>
     </row>
     <row r="10">
@@ -610,25 +610,25 @@
         <v>45906</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>1164.68</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>19.09</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>835.13</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>226.65</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>3200</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>318263</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>52522</v>
       </c>
     </row>
     <row r="11">
@@ -662,25 +662,25 @@
         <v>45908</v>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>1444.65</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1046.02</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>286.55</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1532</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>370924</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>63804</v>
       </c>
     </row>
     <row r="13">
@@ -688,25 +688,25 @@
         <v>45909</v>
       </c>
       <c r="B13" t="n">
-        <v>1433.55</v>
+        <v>390.16</v>
       </c>
       <c r="C13" t="n">
-        <v>22.47</v>
+        <v>6.14</v>
       </c>
       <c r="D13" t="n">
-        <v>1041.48</v>
+        <v>282.22</v>
       </c>
       <c r="E13" t="n">
-        <v>286.9</v>
+        <v>78.22</v>
       </c>
       <c r="F13" t="n">
-        <v>1262</v>
+        <v>459</v>
       </c>
       <c r="G13" t="n">
-        <v>394108</v>
+        <v>100144</v>
       </c>
       <c r="H13" t="n">
-        <v>66411</v>
+        <v>18757</v>
       </c>
     </row>
     <row r="14">
@@ -714,25 +714,25 @@
         <v>45910</v>
       </c>
       <c r="B14" t="n">
-        <v>1542.87</v>
+        <v>1575.06</v>
       </c>
       <c r="C14" t="n">
         <v>24</v>
       </c>
       <c r="D14" t="n">
-        <v>1119.14</v>
+        <v>1142.04</v>
       </c>
       <c r="E14" t="n">
-        <v>304.77</v>
+        <v>319.63</v>
       </c>
       <c r="F14" t="n">
-        <v>1460</v>
+        <v>1477</v>
       </c>
       <c r="G14" t="n">
-        <v>384081</v>
+        <v>453705</v>
       </c>
       <c r="H14" t="n">
-        <v>68700</v>
+        <v>70511</v>
       </c>
     </row>
     <row r="15">
@@ -740,25 +740,25 @@
         <v>45911</v>
       </c>
       <c r="B15" t="n">
-        <v>1427.79</v>
+        <v>1509</v>
       </c>
       <c r="C15" t="n">
         <v>24</v>
       </c>
       <c r="D15" t="n">
-        <v>1038.17</v>
+        <v>1095.65</v>
       </c>
       <c r="E15" t="n">
-        <v>287.13</v>
+        <v>304.46</v>
       </c>
       <c r="F15" t="n">
-        <v>1349</v>
+        <v>1542</v>
       </c>
       <c r="G15" t="n">
-        <v>350110</v>
+        <v>389346</v>
       </c>
       <c r="H15" t="n">
-        <v>64220</v>
+        <v>64230</v>
       </c>
     </row>
     <row r="16">
@@ -766,25 +766,25 @@
         <v>45912</v>
       </c>
       <c r="B16" t="n">
-        <v>1518.94</v>
+        <v>1449.82</v>
       </c>
       <c r="C16" t="n">
         <v>24</v>
       </c>
       <c r="D16" t="n">
-        <v>1108.59</v>
+        <v>1052.89</v>
       </c>
       <c r="E16" t="n">
-        <v>303.05</v>
+        <v>294.86</v>
       </c>
       <c r="F16" t="n">
-        <v>1291</v>
+        <v>1351</v>
       </c>
       <c r="G16" t="n">
-        <v>395379</v>
+        <v>412526</v>
       </c>
       <c r="H16" t="n">
-        <v>69035</v>
+        <v>61988</v>
       </c>
     </row>
     <row r="17">
@@ -792,25 +792,25 @@
         <v>45913</v>
       </c>
       <c r="B17" t="n">
-        <v>178.29</v>
+        <v>1355.12</v>
       </c>
       <c r="C17" t="n">
-        <v>2.87</v>
+        <v>21.25</v>
       </c>
       <c r="D17" t="n">
-        <v>129.7</v>
+        <v>975.88</v>
       </c>
       <c r="E17" t="n">
-        <v>35.75</v>
+        <v>278.43</v>
       </c>
       <c r="F17" t="n">
-        <v>194</v>
+        <v>1242</v>
       </c>
       <c r="G17" t="n">
-        <v>59195</v>
+        <v>342966</v>
       </c>
       <c r="H17" t="n">
-        <v>7915</v>
+        <v>62719</v>
       </c>
     </row>
     <row r="18">
@@ -818,25 +818,25 @@
         <v>45914</v>
       </c>
       <c r="B18" t="n">
-        <v>1608</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1159.03</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
-        <v>318.36</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1484</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>481749</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>72571</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -844,25 +844,25 @@
         <v>45915</v>
       </c>
       <c r="B19" t="n">
-        <v>1508.28</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>1091.16</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>300.13</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>1333</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>389637</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>66527</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -870,25 +870,25 @@
         <v>45916</v>
       </c>
       <c r="B20" t="n">
-        <v>1494.54</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>23.73</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>1086.45</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>293.13</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>1217</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>410361</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>68416</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -896,25 +896,25 @@
         <v>45917</v>
       </c>
       <c r="B21" t="n">
-        <v>1288.51</v>
+        <v>1580.44</v>
       </c>
       <c r="C21" t="n">
-        <v>19.65</v>
+        <v>24</v>
       </c>
       <c r="D21" t="n">
-        <v>930.02</v>
+        <v>1140.26</v>
       </c>
       <c r="E21" t="n">
-        <v>257.02</v>
+        <v>312.88</v>
       </c>
       <c r="F21" t="n">
-        <v>1412</v>
+        <v>1496</v>
       </c>
       <c r="G21" t="n">
-        <v>344624</v>
+        <v>394371</v>
       </c>
       <c r="H21" t="n">
-        <v>56361</v>
+        <v>71657</v>
       </c>
     </row>
     <row r="22">
@@ -922,25 +922,25 @@
         <v>45918</v>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>1428.08</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>1039.21</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>276.42</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>1567</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>378132</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>60290</v>
       </c>
     </row>
     <row r="23">
@@ -948,25 +948,25 @@
         <v>45919</v>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1557.32</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>1139.12</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>305.69</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1544</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>394730</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>65410</v>
       </c>
     </row>
     <row r="24">
@@ -974,25 +974,25 @@
         <v>45920</v>
       </c>
       <c r="B24" t="n">
-        <v>1360.28</v>
+        <v>793.88</v>
       </c>
       <c r="C24" t="n">
-        <v>22.3</v>
+        <v>12.98</v>
       </c>
       <c r="D24" t="n">
-        <v>991.52</v>
+        <v>575.54</v>
       </c>
       <c r="E24" t="n">
-        <v>265.41</v>
+        <v>157.05</v>
       </c>
       <c r="F24" t="n">
-        <v>1425</v>
+        <v>1078</v>
       </c>
       <c r="G24" t="n">
-        <v>352445</v>
+        <v>233124</v>
       </c>
       <c r="H24" t="n">
-        <v>66458</v>
+        <v>35764</v>
       </c>
     </row>
     <row r="25">
@@ -1000,25 +1000,25 @@
         <v>45921</v>
       </c>
       <c r="B25" t="n">
-        <v>1480.86</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>1077.16</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>289.26</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1275</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>392085</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>66249</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1026,25 +1026,25 @@
         <v>45922</v>
       </c>
       <c r="B26" t="n">
-        <v>1294.25</v>
+        <v>1564.92</v>
       </c>
       <c r="C26" t="n">
-        <v>21.39</v>
+        <v>24</v>
       </c>
       <c r="D26" t="n">
-        <v>943.04</v>
+        <v>1139.23</v>
       </c>
       <c r="E26" t="n">
-        <v>258.99</v>
+        <v>300.69</v>
       </c>
       <c r="F26" t="n">
-        <v>1261</v>
+        <v>1562</v>
       </c>
       <c r="G26" t="n">
-        <v>367149</v>
+        <v>406903</v>
       </c>
       <c r="H26" t="n">
-        <v>58574</v>
+        <v>68799</v>
       </c>
     </row>
     <row r="27">
@@ -1052,25 +1052,25 @@
         <v>45923</v>
       </c>
       <c r="B27" t="n">
-        <v>0</v>
+        <v>1448.71</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>23.33</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1050.08</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>285.71</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>1152</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>377387</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>63085</v>
       </c>
     </row>
     <row r="28">
@@ -1078,25 +1078,25 @@
         <v>45924</v>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1391.59</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1011.4</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>281.6</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1388</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>362507</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>68098</v>
       </c>
     </row>
     <row r="29">
@@ -1104,25 +1104,25 @@
         <v>45925</v>
       </c>
       <c r="B29" t="n">
-        <v>0</v>
+        <v>1549.01</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>1122.17</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>313.92</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>1229</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>404755</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>70075</v>
       </c>
     </row>
     <row r="30">
@@ -1130,25 +1130,25 @@
         <v>45926</v>
       </c>
       <c r="B30" t="n">
-        <v>1499.55</v>
+        <v>1352.7</v>
       </c>
       <c r="C30" t="n">
-        <v>24</v>
+        <v>22.7</v>
       </c>
       <c r="D30" t="n">
-        <v>1085.52</v>
+        <v>979.98</v>
       </c>
       <c r="E30" t="n">
-        <v>301.65</v>
+        <v>267.61</v>
       </c>
       <c r="F30" t="n">
-        <v>1474</v>
+        <v>1131</v>
       </c>
       <c r="G30" t="n">
-        <v>379987</v>
+        <v>350227</v>
       </c>
       <c r="H30" t="n">
-        <v>69053</v>
+        <v>61167</v>
       </c>
     </row>
     <row r="31">
@@ -1156,25 +1156,25 @@
         <v>45927</v>
       </c>
       <c r="B31" t="n">
-        <v>1412.59</v>
+        <v>0</v>
       </c>
       <c r="C31" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D31" t="n">
-        <v>1028.53</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
-        <v>276.29</v>
+        <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>1257</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>364942</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>66014</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -1182,25 +1182,25 @@
         <v>45928</v>
       </c>
       <c r="B32" t="n">
-        <v>1473.54</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1082.48</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>303.86</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>1533</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>353842</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>66519</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -1208,25 +1208,25 @@
         <v>45929</v>
       </c>
       <c r="B33" t="n">
-        <v>1480.07</v>
+        <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>1076.7</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>294.36</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>1645</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>416568</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>65290</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -1234,25 +1234,25 @@
         <v>45930</v>
       </c>
       <c r="B34" t="n">
-        <v>808.7</v>
+        <v>857.87</v>
       </c>
       <c r="C34" t="n">
         <v>13.69</v>
       </c>
       <c r="D34" t="n">
-        <v>591.36</v>
+        <v>629.79</v>
       </c>
       <c r="E34" t="n">
-        <v>164.27</v>
+        <v>169.85</v>
       </c>
       <c r="F34" t="n">
-        <v>976</v>
+        <v>901</v>
       </c>
       <c r="G34" t="n">
-        <v>215502</v>
+        <v>234967</v>
       </c>
       <c r="H34" t="n">
-        <v>33949</v>
+        <v>40182</v>
       </c>
     </row>
     <row r="36">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>30245.5</v>
+        <v>28418.05</v>
       </c>
       <c r="C36" t="n">
-        <v>483.72</v>
+        <v>454.55</v>
       </c>
       <c r="D36" t="n">
-        <v>21956.06</v>
+        <v>20577.77</v>
       </c>
       <c r="E36" t="n">
-        <v>5999.52</v>
+        <v>5678.48</v>
       </c>
       <c r="F36" t="n">
-        <v>29061</v>
+        <v>29088</v>
       </c>
       <c r="G36" t="n">
-        <v>7983697</v>
+        <v>7568458</v>
       </c>
       <c r="H36" t="n">
-        <v>1360040</v>
+        <v>1273645</v>
       </c>
     </row>
   </sheetData>
